--- a/datos/multiples_IV.xlsx
+++ b/datos/multiples_IV.xlsx
@@ -446,10 +446,10 @@
         <v>-1</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.833884331560286e-06</v>
+        <v>-1.636452158525249e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.833884331560286e-06</v>
+        <v>-1.636452158525249e-06</v>
       </c>
     </row>
     <row r="3">
@@ -460,10 +460,10 @@
         <v>-0.9797979797979798</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.516482332386715e-06</v>
+        <v>-1.754673247845208e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.516482332386715e-06</v>
+        <v>-1.754673247845208e-06</v>
       </c>
     </row>
     <row r="4">
@@ -474,10 +474,10 @@
         <v>-0.9595959595959596</v>
       </c>
       <c r="C4" t="n">
-        <v>-2.020804903267958e-06</v>
+        <v>-1.62099697297661e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>-2.020804903267958e-06</v>
+        <v>-1.62099697297661e-06</v>
       </c>
     </row>
     <row r="5">
@@ -488,10 +488,10 @@
         <v>-0.9393939393939394</v>
       </c>
       <c r="C5" t="n">
-        <v>-2.004431403485094e-06</v>
+        <v>-2.207436947687934e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.004431403485094e-06</v>
+        <v>-2.207436947687934e-06</v>
       </c>
     </row>
     <row r="6">
@@ -502,10 +502,10 @@
         <v>-0.9191919191919192</v>
       </c>
       <c r="C6" t="n">
-        <v>-2.062449377240561e-06</v>
+        <v>-2.004583999075453e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.062449377240561e-06</v>
+        <v>-2.004583999075453e-06</v>
       </c>
     </row>
     <row r="7">
@@ -516,10 +516,10 @@
         <v>-0.898989898989899</v>
       </c>
       <c r="C7" t="n">
-        <v>-2.153807750008932e-06</v>
+        <v>-2.207005987340971e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.153807750008932e-06</v>
+        <v>-2.207005987340971e-06</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         <v>-0.8787878787878788</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.802033107391586e-06</v>
+        <v>-2.017281711800247e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.802033107391586e-06</v>
+        <v>-2.017281711800247e-06</v>
       </c>
     </row>
     <row r="9">
@@ -544,10 +544,10 @@
         <v>-0.8585858585858586</v>
       </c>
       <c r="C9" t="n">
-        <v>-1.936186438664239e-06</v>
+        <v>-2.26850058438485e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.936186438664239e-06</v>
+        <v>-2.26850058438485e-06</v>
       </c>
     </row>
     <row r="10">
@@ -558,10 +558,10 @@
         <v>-0.8383838383838383</v>
       </c>
       <c r="C10" t="n">
-        <v>-2.037505833002867e-06</v>
+        <v>-1.954843514915349e-06</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.037505833002867e-06</v>
+        <v>-1.954843514915349e-06</v>
       </c>
     </row>
     <row r="11">
@@ -572,10 +572,10 @@
         <v>-0.8181818181818181</v>
       </c>
       <c r="C11" t="n">
-        <v>-1.974992310730579e-06</v>
+        <v>-1.983566382418753e-06</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.974992310730579e-06</v>
+        <v>-1.983566382418753e-06</v>
       </c>
     </row>
     <row r="12">
@@ -586,10 +586,10 @@
         <v>-0.797979797979798</v>
       </c>
       <c r="C12" t="n">
-        <v>-2.050906428268928e-06</v>
+        <v>-1.891709513674777e-06</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.050906428268928e-06</v>
+        <v>-1.891709513674777e-06</v>
       </c>
     </row>
     <row r="13">
@@ -600,10 +600,10 @@
         <v>-0.7777777777777778</v>
       </c>
       <c r="C13" t="n">
-        <v>-2.120412116412068e-06</v>
+        <v>-1.88033409718262e-06</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.120412116412068e-06</v>
+        <v>-1.88033409718262e-06</v>
       </c>
     </row>
     <row r="14">
@@ -614,10 +614,10 @@
         <v>-0.7575757575757576</v>
       </c>
       <c r="C14" t="n">
-        <v>-1.981058173791e-06</v>
+        <v>-1.909255704330645e-06</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.981058173791e-06</v>
+        <v>-1.909255704330645e-06</v>
       </c>
     </row>
     <row r="15">
@@ -628,10 +628,10 @@
         <v>-0.7373737373737373</v>
       </c>
       <c r="C15" t="n">
-        <v>-2.32555404347925e-06</v>
+        <v>-1.922439803177804e-06</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.32555404347925e-06</v>
+        <v>-1.922439803177804e-06</v>
       </c>
     </row>
     <row r="16">
@@ -642,10 +642,10 @@
         <v>-0.7171717171717171</v>
       </c>
       <c r="C16" t="n">
-        <v>-1.838569866271818e-06</v>
+        <v>-1.900165651119219e-06</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.838569866271818e-06</v>
+        <v>-1.900165651119219e-06</v>
       </c>
     </row>
     <row r="17">
@@ -656,10 +656,10 @@
         <v>-0.696969696969697</v>
       </c>
       <c r="C17" t="n">
-        <v>-1.9565405860501e-06</v>
+        <v>-1.512148504162487e-06</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.9565405860501e-06</v>
+        <v>-1.512148504162487e-06</v>
       </c>
     </row>
     <row r="18">
@@ -670,10 +670,10 @@
         <v>-0.6767676767676767</v>
       </c>
       <c r="C18" t="n">
-        <v>-2.014028789392755e-06</v>
+        <v>-1.935992618333445e-06</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.014028789392755e-06</v>
+        <v>-1.935992618333445e-06</v>
       </c>
     </row>
     <row r="19">
@@ -684,10 +684,10 @@
         <v>-0.6565656565656566</v>
       </c>
       <c r="C19" t="n">
-        <v>-2.302982873266765e-06</v>
+        <v>-2.005617400070318e-06</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.302982873266765e-06</v>
+        <v>-2.005617400070318e-06</v>
       </c>
     </row>
     <row r="20">
@@ -698,10 +698,10 @@
         <v>-0.6363636363636364</v>
       </c>
       <c r="C20" t="n">
-        <v>-2.315361746587995e-06</v>
+        <v>-1.538111368334265e-06</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.315361746587995e-06</v>
+        <v>-1.538111368334265e-06</v>
       </c>
     </row>
     <row r="21">
@@ -712,10 +712,10 @@
         <v>-0.6161616161616161</v>
       </c>
       <c r="C21" t="n">
-        <v>-1.780083663328634e-06</v>
+        <v>-2.027231167186312e-06</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.780083663328634e-06</v>
+        <v>-2.027231167186312e-06</v>
       </c>
     </row>
     <row r="22">
@@ -726,10 +726,10 @@
         <v>-0.5959595959595959</v>
       </c>
       <c r="C22" t="n">
-        <v>-2.143415256870065e-06</v>
+        <v>-2.479543387652754e-06</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.143415256870065e-06</v>
+        <v>-2.479543387652754e-06</v>
       </c>
     </row>
     <row r="23">
@@ -740,10 +740,10 @@
         <v>-0.5757575757575757</v>
       </c>
       <c r="C23" t="n">
-        <v>-2.061188017527509e-06</v>
+        <v>-1.983493164002714e-06</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.061188017527509e-06</v>
+        <v>-1.983493164002714e-06</v>
       </c>
     </row>
     <row r="24">
@@ -754,10 +754,10 @@
         <v>-0.5555555555555556</v>
       </c>
       <c r="C24" t="n">
-        <v>-1.971270804851536e-06</v>
+        <v>-1.626756459752337e-06</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.971270804851536e-06</v>
+        <v>-1.626756459752337e-06</v>
       </c>
     </row>
     <row r="25">
@@ -768,10 +768,10 @@
         <v>-0.5353535353535352</v>
       </c>
       <c r="C25" t="n">
-        <v>-2.201502796319581e-06</v>
+        <v>-2.164714899844983e-06</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.201502796319581e-06</v>
+        <v>-2.164714899844983e-06</v>
       </c>
     </row>
     <row r="26">
@@ -782,10 +782,10 @@
         <v>-0.5151515151515151</v>
       </c>
       <c r="C26" t="n">
-        <v>-2.232366299598948e-06</v>
+        <v>-2.009034956212486e-06</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.232366299598948e-06</v>
+        <v>-2.009034956212486e-06</v>
       </c>
     </row>
     <row r="27">
@@ -796,10 +796,10 @@
         <v>-0.4949494949494949</v>
       </c>
       <c r="C27" t="n">
-        <v>-1.774682706747559e-06</v>
+        <v>-1.802792931415998e-06</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.774682706747559e-06</v>
+        <v>-1.802792931415998e-06</v>
       </c>
     </row>
     <row r="28">
@@ -810,10 +810,10 @@
         <v>-0.4747474747474747</v>
       </c>
       <c r="C28" t="n">
-        <v>-1.855328174284529e-06</v>
+        <v>-2.025502003323557e-06</v>
       </c>
       <c r="D28" t="n">
-        <v>-1.855328174284529e-06</v>
+        <v>-2.025502003323557e-06</v>
       </c>
     </row>
     <row r="29">
@@ -824,10 +824,10 @@
         <v>-0.4545454545454545</v>
       </c>
       <c r="C29" t="n">
-        <v>-1.939129462967382e-06</v>
+        <v>-1.828122980125157e-06</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.939129462967382e-06</v>
+        <v>-1.828122980125157e-06</v>
       </c>
     </row>
     <row r="30">
@@ -838,10 +838,10 @@
         <v>-0.4343434343434343</v>
       </c>
       <c r="C30" t="n">
-        <v>-1.624236709365876e-06</v>
+        <v>-1.531905847660171e-06</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.624236709365876e-06</v>
+        <v>-1.531905847660171e-06</v>
       </c>
     </row>
     <row r="31">
@@ -852,10 +852,10 @@
         <v>-0.4141414141414141</v>
       </c>
       <c r="C31" t="n">
-        <v>-1.908449938624446e-06</v>
+        <v>-2.000346570730928e-06</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.908449938624446e-06</v>
+        <v>-2.000346570730928e-06</v>
       </c>
     </row>
     <row r="32">
@@ -866,10 +866,10 @@
         <v>-0.3939393939393939</v>
       </c>
       <c r="C32" t="n">
-        <v>-2.12820220867105e-06</v>
+        <v>-1.816973410859919e-06</v>
       </c>
       <c r="D32" t="n">
-        <v>-2.12820220867105e-06</v>
+        <v>-1.816973410859919e-06</v>
       </c>
     </row>
     <row r="33">
@@ -880,10 +880,10 @@
         <v>-0.3737373737373737</v>
       </c>
       <c r="C33" t="n">
-        <v>-1.890212170965424e-06</v>
+        <v>-1.698968412167003e-06</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.890212170965424e-06</v>
+        <v>-1.698968412167003e-06</v>
       </c>
     </row>
     <row r="34">
@@ -894,10 +894,10 @@
         <v>-0.3535353535353535</v>
       </c>
       <c r="C34" t="n">
-        <v>-1.891572739040107e-06</v>
+        <v>-2.157798743948315e-06</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.891572739040107e-06</v>
+        <v>-2.157798743948315e-06</v>
       </c>
     </row>
     <row r="35">
@@ -908,10 +908,10 @@
         <v>-0.3333333333333333</v>
       </c>
       <c r="C35" t="n">
-        <v>-1.646304196151411e-06</v>
+        <v>-1.761572418921142e-06</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.646304196151411e-06</v>
+        <v>-1.761572418921142e-06</v>
       </c>
     </row>
     <row r="36">
@@ -922,10 +922,10 @@
         <v>-0.313131313131313</v>
       </c>
       <c r="C36" t="n">
-        <v>-1.757087661954315e-06</v>
+        <v>-1.928910385829471e-06</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.757087661954315e-06</v>
+        <v>-1.928910385829471e-06</v>
       </c>
     </row>
     <row r="37">
@@ -936,10 +936,10 @@
         <v>-0.2929292929292928</v>
       </c>
       <c r="C37" t="n">
-        <v>-1.934314186383109e-06</v>
+        <v>-1.620620969409156e-06</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.934314186383109e-06</v>
+        <v>-1.620620969409156e-06</v>
       </c>
     </row>
     <row r="38">
@@ -950,10 +950,10 @@
         <v>-0.2727272727272727</v>
       </c>
       <c r="C38" t="n">
-        <v>-2.13193592860018e-06</v>
+        <v>-1.895027906508048e-06</v>
       </c>
       <c r="D38" t="n">
-        <v>-2.13193592860018e-06</v>
+        <v>-1.895027906508048e-06</v>
       </c>
     </row>
     <row r="39">
@@ -964,10 +964,10 @@
         <v>-0.2525252525252525</v>
       </c>
       <c r="C39" t="n">
-        <v>-1.728769013777084e-06</v>
+        <v>-1.928221084063818e-06</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.728769013777084e-06</v>
+        <v>-1.928221084063818e-06</v>
       </c>
     </row>
     <row r="40">
@@ -978,10 +978,10 @@
         <v>-0.2323232323232323</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.558726081562819e-06</v>
+        <v>-1.955685253963328e-06</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.558726081562819e-06</v>
+        <v>-1.955685253963328e-06</v>
       </c>
     </row>
     <row r="41">
@@ -992,10 +992,10 @@
         <v>-0.212121212121212</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.898524070169357e-06</v>
+        <v>-1.72063698948994e-06</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.898524070169357e-06</v>
+        <v>-1.72063698948994e-06</v>
       </c>
     </row>
     <row r="42">
@@ -1006,10 +1006,10 @@
         <v>-0.1919191919191918</v>
       </c>
       <c r="C42" t="n">
-        <v>-1.338372887984707e-06</v>
+        <v>-1.859608333741323e-06</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.338372887984707e-06</v>
+        <v>-1.859608333741323e-06</v>
       </c>
     </row>
     <row r="43">
@@ -1020,10 +1020,10 @@
         <v>-0.1717171717171716</v>
       </c>
       <c r="C43" t="n">
-        <v>-1.646914721634848e-06</v>
+        <v>-1.319275650109435e-06</v>
       </c>
       <c r="D43" t="n">
-        <v>-1.646914721634848e-06</v>
+        <v>-1.319275650109435e-06</v>
       </c>
     </row>
     <row r="44">
@@ -1034,10 +1034,10 @@
         <v>-0.1515151515151515</v>
       </c>
       <c r="C44" t="n">
-        <v>-1.918626192032228e-06</v>
+        <v>-1.409753338856352e-06</v>
       </c>
       <c r="D44" t="n">
-        <v>-1.918626192032228e-06</v>
+        <v>-1.409753338856352e-06</v>
       </c>
     </row>
     <row r="45">
@@ -1048,10 +1048,10 @@
         <v>-0.1313131313131313</v>
       </c>
       <c r="C45" t="n">
-        <v>-1.563009334848291e-06</v>
+        <v>-1.365192858329166e-06</v>
       </c>
       <c r="D45" t="n">
-        <v>-1.563009334848291e-06</v>
+        <v>-1.365192858329166e-06</v>
       </c>
     </row>
     <row r="46">
@@ -1062,10 +1062,10 @@
         <v>-0.111111111111111</v>
       </c>
       <c r="C46" t="n">
-        <v>-1.500201562695906e-06</v>
+        <v>-1.3212081829219e-06</v>
       </c>
       <c r="D46" t="n">
-        <v>-1.500201562695906e-06</v>
+        <v>-1.3212081829219e-06</v>
       </c>
     </row>
     <row r="47">
@@ -1076,10 +1076,10 @@
         <v>-0.09090909090909083</v>
       </c>
       <c r="C47" t="n">
-        <v>-1.421074347094541e-06</v>
+        <v>-1.574892068628201e-06</v>
       </c>
       <c r="D47" t="n">
-        <v>-1.421074347094541e-06</v>
+        <v>-1.574892068628201e-06</v>
       </c>
     </row>
     <row r="48">
@@ -1090,10 +1090,10 @@
         <v>-0.07070707070707061</v>
       </c>
       <c r="C48" t="n">
-        <v>-9.425221110965188e-07</v>
+        <v>-6.0451639443701e-07</v>
       </c>
       <c r="D48" t="n">
-        <v>-9.425221110965188e-07</v>
+        <v>-6.0451639443701e-07</v>
       </c>
     </row>
     <row r="49">
@@ -1104,10 +1104,10 @@
         <v>-0.05050505050505039</v>
       </c>
       <c r="C49" t="n">
-        <v>-7.392843308450331e-07</v>
+        <v>-9.19726985176425e-07</v>
       </c>
       <c r="D49" t="n">
-        <v>-7.392843308450331e-07</v>
+        <v>-9.19726985176425e-07</v>
       </c>
     </row>
     <row r="50">
@@ -1118,10 +1118,10 @@
         <v>-0.03030303030303028</v>
       </c>
       <c r="C50" t="n">
-        <v>-5.236989748667127e-07</v>
+        <v>-3.991360339972633e-07</v>
       </c>
       <c r="D50" t="n">
-        <v>-5.236989748667127e-07</v>
+        <v>-3.991360339972633e-07</v>
       </c>
     </row>
     <row r="51">
@@ -1132,10 +1132,10 @@
         <v>-0.01010101010101006</v>
       </c>
       <c r="C51" t="n">
-        <v>-1.045691703525202e-07</v>
+        <v>-1.992616111456932e-08</v>
       </c>
       <c r="D51" t="n">
-        <v>-1.045691703525202e-07</v>
+        <v>-1.992616111456932e-08</v>
       </c>
     </row>
     <row r="52">
@@ -1146,10 +1146,10 @@
         <v>0.01010101010101017</v>
       </c>
       <c r="C52" t="n">
-        <v>2.683812951397571e-07</v>
+        <v>1.808548200119853e-07</v>
       </c>
       <c r="D52" t="n">
-        <v>2.683812951397571e-07</v>
+        <v>1.808548200119853e-07</v>
       </c>
     </row>
     <row r="53">
@@ -1160,10 +1160,10 @@
         <v>0.0303030303030305</v>
       </c>
       <c r="C53" t="n">
-        <v>7.36297914662573e-07</v>
+        <v>8.525981823165029e-07</v>
       </c>
       <c r="D53" t="n">
-        <v>7.36297914662573e-07</v>
+        <v>8.525981823165029e-07</v>
       </c>
     </row>
     <row r="54">
@@ -1174,10 +1174,10 @@
         <v>0.05050505050505061</v>
       </c>
       <c r="C54" t="n">
-        <v>1.451756404899327e-06</v>
+        <v>1.11383511582097e-06</v>
       </c>
       <c r="D54" t="n">
-        <v>1.451756404899327e-06</v>
+        <v>1.11383511582097e-06</v>
       </c>
     </row>
     <row r="55">
@@ -1188,10 +1188,10 @@
         <v>0.07070707070707072</v>
       </c>
       <c r="C55" t="n">
-        <v>2.269811384327674e-06</v>
+        <v>1.73738549411064e-06</v>
       </c>
       <c r="D55" t="n">
-        <v>2.269811384327674e-06</v>
+        <v>1.73738549411064e-06</v>
       </c>
     </row>
     <row r="56">
@@ -1202,10 +1202,10 @@
         <v>0.09090909090909105</v>
       </c>
       <c r="C56" t="n">
-        <v>3.045400007286663e-06</v>
+        <v>3.125216152899807e-06</v>
       </c>
       <c r="D56" t="n">
-        <v>3.045400007286663e-06</v>
+        <v>3.125216152899807e-06</v>
       </c>
     </row>
     <row r="57">
@@ -1216,10 +1216,10 @@
         <v>0.1111111111111112</v>
       </c>
       <c r="C57" t="n">
-        <v>4.311801249710025e-06</v>
+        <v>4.098361886842276e-06</v>
       </c>
       <c r="D57" t="n">
-        <v>4.311801249710025e-06</v>
+        <v>4.098361886842276e-06</v>
       </c>
     </row>
     <row r="58">
@@ -1230,10 +1230,10 @@
         <v>0.1313131313131315</v>
       </c>
       <c r="C58" t="n">
-        <v>5.113877632755933e-06</v>
+        <v>5.549792581675445e-06</v>
       </c>
       <c r="D58" t="n">
-        <v>5.113877632755933e-06</v>
+        <v>5.549792581675445e-06</v>
       </c>
     </row>
     <row r="59">
@@ -1244,10 +1244,10 @@
         <v>0.1515151515151516</v>
       </c>
       <c r="C59" t="n">
-        <v>7.285995211050194e-06</v>
+        <v>7.270216411266156e-06</v>
       </c>
       <c r="D59" t="n">
-        <v>7.285995211050194e-06</v>
+        <v>7.270216411266156e-06</v>
       </c>
     </row>
     <row r="60">
@@ -1258,10 +1258,10 @@
         <v>0.1717171717171717</v>
       </c>
       <c r="C60" t="n">
-        <v>9.030423973407028e-06</v>
+        <v>9.003892450355395e-06</v>
       </c>
       <c r="D60" t="n">
-        <v>9.030423973407028e-06</v>
+        <v>9.003892450355395e-06</v>
       </c>
     </row>
     <row r="61">
@@ -1272,10 +1272,10 @@
         <v>0.191919191919192</v>
       </c>
       <c r="C61" t="n">
-        <v>1.170874742596345e-05</v>
+        <v>1.160449428522706e-05</v>
       </c>
       <c r="D61" t="n">
-        <v>1.170874742596345e-05</v>
+        <v>1.160449428522706e-05</v>
       </c>
     </row>
     <row r="62">
@@ -1286,10 +1286,10 @@
         <v>0.2121212121212122</v>
       </c>
       <c r="C62" t="n">
-        <v>1.523205304140178e-05</v>
+        <v>1.475147635287789e-05</v>
       </c>
       <c r="D62" t="n">
-        <v>1.523205304140178e-05</v>
+        <v>1.475147635287789e-05</v>
       </c>
     </row>
     <row r="63">
@@ -1300,10 +1300,10 @@
         <v>0.2323232323232325</v>
       </c>
       <c r="C63" t="n">
-        <v>1.845668101086447e-05</v>
+        <v>1.838099940959834e-05</v>
       </c>
       <c r="D63" t="n">
-        <v>1.845668101086447e-05</v>
+        <v>1.838099940959834e-05</v>
       </c>
     </row>
     <row r="64">
@@ -1314,10 +1314,10 @@
         <v>0.2525252525252526</v>
       </c>
       <c r="C64" t="n">
-        <v>2.310007851685004e-05</v>
+        <v>2.283152857261598e-05</v>
       </c>
       <c r="D64" t="n">
-        <v>2.310007851685004e-05</v>
+        <v>2.283152857261598e-05</v>
       </c>
     </row>
     <row r="65">
@@ -1328,10 +1328,10 @@
         <v>0.2727272727272729</v>
       </c>
       <c r="C65" t="n">
-        <v>2.848154662245354e-05</v>
+        <v>2.867891267740074e-05</v>
       </c>
       <c r="D65" t="n">
-        <v>2.848154662245354e-05</v>
+        <v>2.867891267740074e-05</v>
       </c>
     </row>
     <row r="66">
@@ -1342,10 +1342,10 @@
         <v>0.292929292929293</v>
       </c>
       <c r="C66" t="n">
-        <v>3.571071127469885e-05</v>
+        <v>3.539768343232192e-05</v>
       </c>
       <c r="D66" t="n">
-        <v>3.571071127469885e-05</v>
+        <v>3.539768343232192e-05</v>
       </c>
     </row>
     <row r="67">
@@ -1356,10 +1356,10 @@
         <v>0.3131313131313131</v>
       </c>
       <c r="C67" t="n">
-        <v>4.365386809920926e-05</v>
+        <v>4.402698812895e-05</v>
       </c>
       <c r="D67" t="n">
-        <v>4.365386809920926e-05</v>
+        <v>4.402698812895e-05</v>
       </c>
     </row>
     <row r="68">
@@ -1370,10 +1370,10 @@
         <v>0.3333333333333335</v>
       </c>
       <c r="C68" t="n">
-        <v>5.375730643860089e-05</v>
+        <v>5.392958138709982e-05</v>
       </c>
       <c r="D68" t="n">
-        <v>5.375730643860089e-05</v>
+        <v>5.392958138709982e-05</v>
       </c>
     </row>
     <row r="69">
@@ -1384,10 +1384,10 @@
         <v>0.3535353535353536</v>
       </c>
       <c r="C69" t="n">
-        <v>6.661465280026676e-05</v>
+        <v>6.655642361756346e-05</v>
       </c>
       <c r="D69" t="n">
-        <v>6.661465280026676e-05</v>
+        <v>6.655642361756346e-05</v>
       </c>
     </row>
     <row r="70">
@@ -1398,10 +1398,10 @@
         <v>0.3737373737373739</v>
       </c>
       <c r="C70" t="n">
-        <v>8.201985904521214e-05</v>
+        <v>8.190102498436747e-05</v>
       </c>
       <c r="D70" t="n">
-        <v>8.201985904521214e-05</v>
+        <v>8.190102498436747e-05</v>
       </c>
     </row>
     <row r="71">
@@ -1412,10 +1412,10 @@
         <v>0.393939393939394</v>
       </c>
       <c r="C71" t="n">
-        <v>0.0001011371360298909</v>
+        <v>0.0001009121026161246</v>
       </c>
       <c r="D71" t="n">
-        <v>0.0001011371360298909</v>
+        <v>0.0001009121026161246</v>
       </c>
     </row>
     <row r="72">
@@ -1426,10 +1426,10 @@
         <v>0.4141414141414144</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0001240805886550052</v>
+        <v>0.000123835561085966</v>
       </c>
       <c r="D72" t="n">
-        <v>0.0001240805886550052</v>
+        <v>0.000123835561085966</v>
       </c>
     </row>
     <row r="73">
@@ -1440,10 +1440,10 @@
         <v>0.4343434343434345</v>
       </c>
       <c r="C73" t="n">
-        <v>0.0001521324668323775</v>
+        <v>0.0001519471079867747</v>
       </c>
       <c r="D73" t="n">
-        <v>0.0001521324668323775</v>
+        <v>0.0001519471079867747</v>
       </c>
     </row>
     <row r="74">
@@ -1454,10 +1454,10 @@
         <v>0.4545454545454546</v>
       </c>
       <c r="C74" t="n">
-        <v>0.0001862254164801958</v>
+        <v>0.0001863871311902533</v>
       </c>
       <c r="D74" t="n">
-        <v>0.0001862254164801958</v>
+        <v>0.0001863871311902533</v>
       </c>
     </row>
     <row r="75">
@@ -1468,10 +1468,10 @@
         <v>0.4747474747474749</v>
       </c>
       <c r="C75" t="n">
-        <v>0.0002284817458601223</v>
+        <v>0.0002284395034810829</v>
       </c>
       <c r="D75" t="n">
-        <v>0.0002284817458601223</v>
+        <v>0.0002284395034810829</v>
       </c>
     </row>
     <row r="76">
@@ -1482,10 +1482,10 @@
         <v>0.494949494949495</v>
       </c>
       <c r="C76" t="n">
-        <v>0.000280176157633655</v>
+        <v>0.0002803934575444</v>
       </c>
       <c r="D76" t="n">
-        <v>0.000280176157633655</v>
+        <v>0.0002803934575444</v>
       </c>
     </row>
     <row r="77">
@@ -1496,10 +1496,10 @@
         <v>0.5151515151515154</v>
       </c>
       <c r="C77" t="n">
-        <v>0.0003434259504865634</v>
+        <v>0.0003432804583753863</v>
       </c>
       <c r="D77" t="n">
-        <v>0.0003434259504865634</v>
+        <v>0.0003432804583753863</v>
       </c>
     </row>
     <row r="78">
@@ -1510,10 +1510,10 @@
         <v>0.5353535353535355</v>
       </c>
       <c r="C78" t="n">
-        <v>0.000420993114311553</v>
+        <v>0.0004204230526674805</v>
       </c>
       <c r="D78" t="n">
-        <v>0.000420993114311553</v>
+        <v>0.0004204230526674805</v>
       </c>
     </row>
     <row r="79">
@@ -1524,10 +1524,10 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="C79" t="n">
-        <v>0.0005155236178160574</v>
+        <v>0.0005154887857214339</v>
       </c>
       <c r="D79" t="n">
-        <v>0.0005155236178160574</v>
+        <v>0.0005154887857214339</v>
       </c>
     </row>
     <row r="80">
@@ -1538,10 +1538,10 @@
         <v>0.5757575757575759</v>
       </c>
       <c r="C80" t="n">
-        <v>0.0006313749354090055</v>
+        <v>0.0006311584152654783</v>
       </c>
       <c r="D80" t="n">
-        <v>0.0006313749354090055</v>
+        <v>0.0006311584152654783</v>
       </c>
     </row>
     <row r="81">
@@ -1552,10 +1552,10 @@
         <v>0.595959595959596</v>
       </c>
       <c r="C81" t="n">
-        <v>0.0007729185049023427</v>
+        <v>0.0007728510181668379</v>
       </c>
       <c r="D81" t="n">
-        <v>0.0007729185049023427</v>
+        <v>0.0007728510181668379</v>
       </c>
     </row>
     <row r="82">
@@ -1566,10 +1566,10 @@
         <v>0.6161616161616164</v>
       </c>
       <c r="C82" t="n">
-        <v>0.0009461492052610735</v>
+        <v>0.000946312203622447</v>
       </c>
       <c r="D82" t="n">
-        <v>0.0009461492052610735</v>
+        <v>0.000946312203622447</v>
       </c>
     </row>
     <row r="83">
@@ -1580,10 +1580,10 @@
         <v>0.6363636363636365</v>
       </c>
       <c r="C83" t="n">
-        <v>0.001158661976835256</v>
+        <v>0.001158447162482619</v>
       </c>
       <c r="D83" t="n">
-        <v>0.001158661976835256</v>
+        <v>0.001158447162482619</v>
       </c>
     </row>
     <row r="84">
@@ -1594,10 +1594,10 @@
         <v>0.6565656565656568</v>
       </c>
       <c r="C84" t="n">
-        <v>0.001418430098498226</v>
+        <v>0.001418455920629685</v>
       </c>
       <c r="D84" t="n">
-        <v>0.001418430098498226</v>
+        <v>0.001418455920629685</v>
       </c>
     </row>
     <row r="85">
@@ -1608,10 +1608,10 @@
         <v>0.6767676767676769</v>
       </c>
       <c r="C85" t="n">
-        <v>0.001736516938874451</v>
+        <v>0.001736607696385914</v>
       </c>
       <c r="D85" t="n">
-        <v>0.001736516938874451</v>
+        <v>0.001736607696385914</v>
       </c>
     </row>
     <row r="86">
@@ -1622,10 +1622,10 @@
         <v>0.696969696969697</v>
       </c>
       <c r="C86" t="n">
-        <v>0.002125573459421298</v>
+        <v>0.002125779352700327</v>
       </c>
       <c r="D86" t="n">
-        <v>0.002125573459421298</v>
+        <v>0.002125779352700327</v>
       </c>
     </row>
     <row r="87">
@@ -1636,10 +1636,10 @@
         <v>0.7171717171717173</v>
       </c>
       <c r="C87" t="n">
-        <v>0.00260198815624682</v>
+        <v>0.002601783646772193</v>
       </c>
       <c r="D87" t="n">
-        <v>0.00260198815624682</v>
+        <v>0.002601783646772193</v>
       </c>
     </row>
     <row r="88">
@@ -1650,10 +1650,10 @@
         <v>0.7373737373737375</v>
       </c>
       <c r="C88" t="n">
-        <v>0.00318525739339658</v>
+        <v>0.003185078652632825</v>
       </c>
       <c r="D88" t="n">
-        <v>0.00318525739339658</v>
+        <v>0.003185078652632825</v>
       </c>
     </row>
     <row r="89">
@@ -1664,10 +1664,10 @@
         <v>0.7575757575757578</v>
       </c>
       <c r="C89" t="n">
-        <v>0.003899124431825942</v>
+        <v>0.003898673210266907</v>
       </c>
       <c r="D89" t="n">
-        <v>0.003899124431825942</v>
+        <v>0.003898673210266907</v>
       </c>
     </row>
     <row r="90">
@@ -1678,10 +1678,10 @@
         <v>0.7777777777777779</v>
       </c>
       <c r="C90" t="n">
-        <v>0.00477166723295772</v>
+        <v>0.004771849070328257</v>
       </c>
       <c r="D90" t="n">
-        <v>0.00477166723295772</v>
+        <v>0.004771849070328257</v>
       </c>
     </row>
     <row r="91">
@@ -1692,10 +1692,10 @@
         <v>0.7979797979797982</v>
       </c>
       <c r="C91" t="n">
-        <v>0.005840675911008363</v>
+        <v>0.005841024600406635</v>
       </c>
       <c r="D91" t="n">
-        <v>0.005840675911008363</v>
+        <v>0.005841024600406635</v>
       </c>
     </row>
     <row r="92">
@@ -1706,10 +1706,10 @@
         <v>0.8181818181818183</v>
       </c>
       <c r="C92" t="n">
-        <v>0.007148424612324511</v>
+        <v>0.007148508534971624</v>
       </c>
       <c r="D92" t="n">
-        <v>0.007148424612324511</v>
+        <v>0.007148508534971624</v>
       </c>
     </row>
     <row r="93">
@@ -1720,10 +1720,10 @@
         <v>0.8383838383838385</v>
       </c>
       <c r="C93" t="n">
-        <v>0.008750034056273139</v>
+        <v>0.008749587284016622</v>
       </c>
       <c r="D93" t="n">
-        <v>0.008750034056273139</v>
+        <v>0.008749587284016622</v>
       </c>
     </row>
     <row r="94">
@@ -1734,10 +1734,10 @@
         <v>0.8585858585858588</v>
       </c>
       <c r="C94" t="n">
-        <v>0.01070875425603511</v>
+        <v>0.01070886720236716</v>
       </c>
       <c r="D94" t="n">
-        <v>0.01070875425603511</v>
+        <v>0.01070886720236716</v>
       </c>
     </row>
     <row r="95">
@@ -1748,10 +1748,10 @@
         <v>0.8787878787878789</v>
       </c>
       <c r="C95" t="n">
-        <v>0.01310649097461735</v>
+        <v>0.01310667710960612</v>
       </c>
       <c r="D95" t="n">
-        <v>0.01310649097461735</v>
+        <v>0.01310667710960612</v>
       </c>
     </row>
     <row r="96">
@@ -1762,10 +1762,10 @@
         <v>0.8989898989898992</v>
       </c>
       <c r="C96" t="n">
-        <v>0.01604141321286135</v>
+        <v>0.0160415012852845</v>
       </c>
       <c r="D96" t="n">
-        <v>0.01604141321286135</v>
+        <v>0.0160415012852845</v>
       </c>
     </row>
     <row r="97">
@@ -1776,10 +1776,10 @@
         <v>0.9191919191919193</v>
       </c>
       <c r="C97" t="n">
-        <v>0.01963314457335982</v>
+        <v>0.01963309229947683</v>
       </c>
       <c r="D97" t="n">
-        <v>0.01963314457335982</v>
+        <v>0.01963309229947683</v>
       </c>
     </row>
     <row r="98">
@@ -1790,10 +1790,10 @@
         <v>0.9393939393939394</v>
       </c>
       <c r="C98" t="n">
-        <v>0.02402848139870028</v>
+        <v>0.02402883572353023</v>
       </c>
       <c r="D98" t="n">
-        <v>0.02402848139870028</v>
+        <v>0.02402883572353023</v>
       </c>
     </row>
     <row r="99">
@@ -1804,10 +1804,10 @@
         <v>0.9595959595959598</v>
       </c>
       <c r="C99" t="n">
-        <v>0.02940856590471038</v>
+        <v>0.0294083192729611</v>
       </c>
       <c r="D99" t="n">
-        <v>0.02940856590471038</v>
+        <v>0.0294083192729611</v>
       </c>
     </row>
     <row r="100">
@@ -1818,10 +1818,10 @@
         <v>0.9797979797979799</v>
       </c>
       <c r="C100" t="n">
-        <v>0.03599257698444778</v>
+        <v>0.03599246065959427</v>
       </c>
       <c r="D100" t="n">
-        <v>0.03599257698444778</v>
+        <v>0.03599246065959427</v>
       </c>
     </row>
     <row r="101">
@@ -1832,10 +1832,10 @@
         <v>1</v>
       </c>
       <c r="C101" t="n">
-        <v>0.04405088029491804</v>
+        <v>0.04405069569657915</v>
       </c>
       <c r="D101" t="n">
-        <v>0.04405088029491804</v>
+        <v>0.04405069569657915</v>
       </c>
     </row>
   </sheetData>

--- a/datos/multiples_IV.xlsx
+++ b/datos/multiples_IV.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="datos_IV" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -446,10 +447,10 @@
         <v>-1</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.636452158525249e-06</v>
+        <v>-1.989288358910992e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.636452158525249e-06</v>
+        <v>-1.989288358910992e-06</v>
       </c>
     </row>
     <row r="3">
@@ -460,10 +461,10 @@
         <v>-0.9797979797979798</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.754673247845208e-06</v>
+        <v>-2.031958049790326e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.754673247845208e-06</v>
+        <v>-2.031958049790326e-06</v>
       </c>
     </row>
     <row r="4">
@@ -474,10 +475,10 @@
         <v>-0.9595959595959596</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.62099697297661e-06</v>
+        <v>-1.807820331599974e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.62099697297661e-06</v>
+        <v>-1.807820331599974e-06</v>
       </c>
     </row>
     <row r="5">
@@ -488,10 +489,10 @@
         <v>-0.9393939393939394</v>
       </c>
       <c r="C5" t="n">
-        <v>-2.207436947687934e-06</v>
+        <v>-1.836652810425641e-06</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.207436947687934e-06</v>
+        <v>-1.836652810425641e-06</v>
       </c>
     </row>
     <row r="6">
@@ -502,10 +503,10 @@
         <v>-0.9191919191919192</v>
       </c>
       <c r="C6" t="n">
-        <v>-2.004583999075453e-06</v>
+        <v>-2.117823742824176e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.004583999075453e-06</v>
+        <v>-2.117823742824176e-06</v>
       </c>
     </row>
     <row r="7">
@@ -516,10 +517,10 @@
         <v>-0.898989898989899</v>
       </c>
       <c r="C7" t="n">
-        <v>-2.207005987340971e-06</v>
+        <v>-1.922505389976598e-06</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.207005987340971e-06</v>
+        <v>-1.922505389976598e-06</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +531,10 @@
         <v>-0.8787878787878788</v>
       </c>
       <c r="C8" t="n">
-        <v>-2.017281711800247e-06</v>
+        <v>-1.762748198457116e-06</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.017281711800247e-06</v>
+        <v>-1.762748198457116e-06</v>
       </c>
     </row>
     <row r="9">
@@ -544,10 +545,10 @@
         <v>-0.8585858585858586</v>
       </c>
       <c r="C9" t="n">
-        <v>-2.26850058438485e-06</v>
+        <v>-2.425988479698651e-06</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.26850058438485e-06</v>
+        <v>-2.425988479698651e-06</v>
       </c>
     </row>
     <row r="10">
@@ -558,10 +559,10 @@
         <v>-0.8383838383838383</v>
       </c>
       <c r="C10" t="n">
-        <v>-1.954843514915349e-06</v>
+        <v>-2.225153260574953e-06</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.954843514915349e-06</v>
+        <v>-2.225153260574953e-06</v>
       </c>
     </row>
     <row r="11">
@@ -572,10 +573,10 @@
         <v>-0.8181818181818181</v>
       </c>
       <c r="C11" t="n">
-        <v>-1.983566382418753e-06</v>
+        <v>-2.0176678816081e-06</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.983566382418753e-06</v>
+        <v>-2.0176678816081e-06</v>
       </c>
     </row>
     <row r="12">
@@ -586,10 +587,10 @@
         <v>-0.797979797979798</v>
       </c>
       <c r="C12" t="n">
-        <v>-1.891709513674777e-06</v>
+        <v>-2.113056528473606e-06</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.891709513674777e-06</v>
+        <v>-2.113056528473606e-06</v>
       </c>
     </row>
     <row r="13">
@@ -600,10 +601,10 @@
         <v>-0.7777777777777778</v>
       </c>
       <c r="C13" t="n">
-        <v>-1.88033409718262e-06</v>
+        <v>-2.328472229512787e-06</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.88033409718262e-06</v>
+        <v>-2.328472229512787e-06</v>
       </c>
     </row>
     <row r="14">
@@ -614,10 +615,10 @@
         <v>-0.7575757575757576</v>
       </c>
       <c r="C14" t="n">
-        <v>-1.909255704330645e-06</v>
+        <v>-2.044287432109971e-06</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.909255704330645e-06</v>
+        <v>-2.044287432109971e-06</v>
       </c>
     </row>
     <row r="15">
@@ -628,10 +629,10 @@
         <v>-0.7373737373737373</v>
       </c>
       <c r="C15" t="n">
-        <v>-1.922439803177804e-06</v>
+        <v>-2.230761136963488e-06</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.922439803177804e-06</v>
+        <v>-2.230761136963488e-06</v>
       </c>
     </row>
     <row r="16">
@@ -642,10 +643,10 @@
         <v>-0.7171717171717171</v>
       </c>
       <c r="C16" t="n">
-        <v>-1.900165651119219e-06</v>
+        <v>-2.164860757132963e-06</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.900165651119219e-06</v>
+        <v>-2.164860757132963e-06</v>
       </c>
     </row>
     <row r="17">
@@ -656,10 +657,10 @@
         <v>-0.696969696969697</v>
       </c>
       <c r="C17" t="n">
-        <v>-1.512148504162487e-06</v>
+        <v>-1.933941832240441e-06</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.512148504162487e-06</v>
+        <v>-1.933941832240441e-06</v>
       </c>
     </row>
     <row r="18">
@@ -670,10 +671,10 @@
         <v>-0.6767676767676767</v>
       </c>
       <c r="C18" t="n">
-        <v>-1.935992618333445e-06</v>
+        <v>-2.086315280156268e-06</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.935992618333445e-06</v>
+        <v>-2.086315280156268e-06</v>
       </c>
     </row>
     <row r="19">
@@ -684,10 +685,10 @@
         <v>-0.6565656565656566</v>
       </c>
       <c r="C19" t="n">
-        <v>-2.005617400070318e-06</v>
+        <v>-1.706693741162482e-06</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.005617400070318e-06</v>
+        <v>-1.706693741162482e-06</v>
       </c>
     </row>
     <row r="20">
@@ -698,10 +699,10 @@
         <v>-0.6363636363636364</v>
       </c>
       <c r="C20" t="n">
-        <v>-1.538111368334265e-06</v>
+        <v>-1.881009450840279e-06</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.538111368334265e-06</v>
+        <v>-1.881009450840279e-06</v>
       </c>
     </row>
     <row r="21">
@@ -712,10 +713,10 @@
         <v>-0.6161616161616161</v>
       </c>
       <c r="C21" t="n">
-        <v>-2.027231167186312e-06</v>
+        <v>-1.999168188600938e-06</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.027231167186312e-06</v>
+        <v>-1.999168188600938e-06</v>
       </c>
     </row>
     <row r="22">
@@ -726,10 +727,10 @@
         <v>-0.5959595959595959</v>
       </c>
       <c r="C22" t="n">
-        <v>-2.479543387652754e-06</v>
+        <v>-2.339731865966754e-06</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.479543387652754e-06</v>
+        <v>-2.339731865966754e-06</v>
       </c>
     </row>
     <row r="23">
@@ -740,10 +741,10 @@
         <v>-0.5757575757575757</v>
       </c>
       <c r="C23" t="n">
-        <v>-1.983493164002714e-06</v>
+        <v>-2.387791781416749e-06</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.983493164002714e-06</v>
+        <v>-2.387791781416749e-06</v>
       </c>
     </row>
     <row r="24">
@@ -754,10 +755,10 @@
         <v>-0.5555555555555556</v>
       </c>
       <c r="C24" t="n">
-        <v>-1.626756459752337e-06</v>
+        <v>-1.984913014985858e-06</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.626756459752337e-06</v>
+        <v>-1.984913014985858e-06</v>
       </c>
     </row>
     <row r="25">
@@ -768,10 +769,10 @@
         <v>-0.5353535353535352</v>
       </c>
       <c r="C25" t="n">
-        <v>-2.164714899844983e-06</v>
+        <v>-1.825429152531315e-06</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.164714899844983e-06</v>
+        <v>-1.825429152531315e-06</v>
       </c>
     </row>
     <row r="26">
@@ -782,10 +783,10 @@
         <v>-0.5151515151515151</v>
       </c>
       <c r="C26" t="n">
-        <v>-2.009034956212486e-06</v>
+        <v>-2.110922823199467e-06</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.009034956212486e-06</v>
+        <v>-2.110922823199467e-06</v>
       </c>
     </row>
     <row r="27">
@@ -796,10 +797,10 @@
         <v>-0.4949494949494949</v>
       </c>
       <c r="C27" t="n">
-        <v>-1.802792931415998e-06</v>
+        <v>-1.656298221532684e-06</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.802792931415998e-06</v>
+        <v>-1.656298221532684e-06</v>
       </c>
     </row>
     <row r="28">
@@ -810,10 +811,10 @@
         <v>-0.4747474747474747</v>
       </c>
       <c r="C28" t="n">
-        <v>-2.025502003323557e-06</v>
+        <v>-2.212460907261241e-06</v>
       </c>
       <c r="D28" t="n">
-        <v>-2.025502003323557e-06</v>
+        <v>-2.212460907261241e-06</v>
       </c>
     </row>
     <row r="29">
@@ -824,10 +825,10 @@
         <v>-0.4545454545454545</v>
       </c>
       <c r="C29" t="n">
-        <v>-1.828122980125157e-06</v>
+        <v>-2.366964268252118e-06</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.828122980125157e-06</v>
+        <v>-2.366964268252118e-06</v>
       </c>
     </row>
     <row r="30">
@@ -838,10 +839,10 @@
         <v>-0.4343434343434343</v>
       </c>
       <c r="C30" t="n">
-        <v>-1.531905847660171e-06</v>
+        <v>-2.122892931182688e-06</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.531905847660171e-06</v>
+        <v>-2.122892931182688e-06</v>
       </c>
     </row>
     <row r="31">
@@ -852,10 +853,10 @@
         <v>-0.4141414141414141</v>
       </c>
       <c r="C31" t="n">
-        <v>-2.000346570730928e-06</v>
+        <v>-2.005397126079276e-06</v>
       </c>
       <c r="D31" t="n">
-        <v>-2.000346570730928e-06</v>
+        <v>-2.005397126079276e-06</v>
       </c>
     </row>
     <row r="32">
@@ -866,10 +867,10 @@
         <v>-0.3939393939393939</v>
       </c>
       <c r="C32" t="n">
-        <v>-1.816973410859919e-06</v>
+        <v>-2.289876365002994e-06</v>
       </c>
       <c r="D32" t="n">
-        <v>-1.816973410859919e-06</v>
+        <v>-2.289876365002994e-06</v>
       </c>
     </row>
     <row r="33">
@@ -880,10 +881,10 @@
         <v>-0.3737373737373737</v>
       </c>
       <c r="C33" t="n">
-        <v>-1.698968412167003e-06</v>
+        <v>-1.933267190333845e-06</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.698968412167003e-06</v>
+        <v>-1.933267190333845e-06</v>
       </c>
     </row>
     <row r="34">
@@ -894,10 +895,10 @@
         <v>-0.3535353535353535</v>
       </c>
       <c r="C34" t="n">
-        <v>-2.157798743948315e-06</v>
+        <v>-1.91547397518715e-06</v>
       </c>
       <c r="D34" t="n">
-        <v>-2.157798743948315e-06</v>
+        <v>-1.91547397518715e-06</v>
       </c>
     </row>
     <row r="35">
@@ -908,10 +909,10 @@
         <v>-0.3333333333333333</v>
       </c>
       <c r="C35" t="n">
-        <v>-1.761572418921142e-06</v>
+        <v>-2.245373222560387e-06</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.761572418921142e-06</v>
+        <v>-2.245373222560387e-06</v>
       </c>
     </row>
     <row r="36">
@@ -922,10 +923,10 @@
         <v>-0.313131313131313</v>
       </c>
       <c r="C36" t="n">
-        <v>-1.928910385829471e-06</v>
+        <v>-1.657587326389526e-06</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.928910385829471e-06</v>
+        <v>-1.657587326389526e-06</v>
       </c>
     </row>
     <row r="37">
@@ -936,10 +937,10 @@
         <v>-0.2929292929292928</v>
       </c>
       <c r="C37" t="n">
-        <v>-1.620620969409156e-06</v>
+        <v>-2.10568936176364e-06</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.620620969409156e-06</v>
+        <v>-2.10568936176364e-06</v>
       </c>
     </row>
     <row r="38">
@@ -950,10 +951,10 @@
         <v>-0.2727272727272727</v>
       </c>
       <c r="C38" t="n">
-        <v>-1.895027906508048e-06</v>
+        <v>-1.823590578997594e-06</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.895027906508048e-06</v>
+        <v>-1.823590578997594e-06</v>
       </c>
     </row>
     <row r="39">
@@ -964,10 +965,10 @@
         <v>-0.2525252525252525</v>
       </c>
       <c r="C39" t="n">
-        <v>-1.928221084063818e-06</v>
+        <v>-1.899316397190773e-06</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.928221084063818e-06</v>
+        <v>-1.899316397190773e-06</v>
       </c>
     </row>
     <row r="40">
@@ -978,10 +979,10 @@
         <v>-0.2323232323232323</v>
       </c>
       <c r="C40" t="n">
-        <v>-1.955685253963328e-06</v>
+        <v>-1.8271069553072e-06</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.955685253963328e-06</v>
+        <v>-1.8271069553072e-06</v>
       </c>
     </row>
     <row r="41">
@@ -992,10 +993,10 @@
         <v>-0.212121212121212</v>
       </c>
       <c r="C41" t="n">
-        <v>-1.72063698948994e-06</v>
+        <v>-1.594062970464411e-06</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.72063698948994e-06</v>
+        <v>-1.594062970464411e-06</v>
       </c>
     </row>
     <row r="42">
@@ -1006,10 +1007,10 @@
         <v>-0.1919191919191918</v>
       </c>
       <c r="C42" t="n">
-        <v>-1.859608333741323e-06</v>
+        <v>-1.313265033860147e-06</v>
       </c>
       <c r="D42" t="n">
-        <v>-1.859608333741323e-06</v>
+        <v>-1.313265033860147e-06</v>
       </c>
     </row>
     <row r="43">
@@ -1020,10 +1021,10 @@
         <v>-0.1717171717171716</v>
       </c>
       <c r="C43" t="n">
-        <v>-1.319275650109435e-06</v>
+        <v>-1.612428327042971e-06</v>
       </c>
       <c r="D43" t="n">
-        <v>-1.319275650109435e-06</v>
+        <v>-1.612428327042971e-06</v>
       </c>
     </row>
     <row r="44">
@@ -1034,10 +1035,10 @@
         <v>-0.1515151515151515</v>
       </c>
       <c r="C44" t="n">
-        <v>-1.409753338856352e-06</v>
+        <v>-1.228337145254858e-06</v>
       </c>
       <c r="D44" t="n">
-        <v>-1.409753338856352e-06</v>
+        <v>-1.228337145254858e-06</v>
       </c>
     </row>
     <row r="45">
@@ -1048,10 +1049,10 @@
         <v>-0.1313131313131313</v>
       </c>
       <c r="C45" t="n">
-        <v>-1.365192858329166e-06</v>
+        <v>-1.8641083004055e-06</v>
       </c>
       <c r="D45" t="n">
-        <v>-1.365192858329166e-06</v>
+        <v>-1.8641083004055e-06</v>
       </c>
     </row>
     <row r="46">
@@ -1062,10 +1063,10 @@
         <v>-0.111111111111111</v>
       </c>
       <c r="C46" t="n">
-        <v>-1.3212081829219e-06</v>
+        <v>-1.150313280174724e-06</v>
       </c>
       <c r="D46" t="n">
-        <v>-1.3212081829219e-06</v>
+        <v>-1.150313280174724e-06</v>
       </c>
     </row>
     <row r="47">
@@ -1076,10 +1077,10 @@
         <v>-0.09090909090909083</v>
       </c>
       <c r="C47" t="n">
-        <v>-1.574892068628201e-06</v>
+        <v>-1.198460637039772e-06</v>
       </c>
       <c r="D47" t="n">
-        <v>-1.574892068628201e-06</v>
+        <v>-1.198460637039772e-06</v>
       </c>
     </row>
     <row r="48">
@@ -1090,10 +1091,10 @@
         <v>-0.07070707070707061</v>
       </c>
       <c r="C48" t="n">
-        <v>-6.0451639443701e-07</v>
+        <v>-1.303700184298083e-06</v>
       </c>
       <c r="D48" t="n">
-        <v>-6.0451639443701e-07</v>
+        <v>-1.303700184298083e-06</v>
       </c>
     </row>
     <row r="49">
@@ -1104,10 +1105,10 @@
         <v>-0.05050505050505039</v>
       </c>
       <c r="C49" t="n">
-        <v>-9.19726985176425e-07</v>
+        <v>-5.43066003764652e-07</v>
       </c>
       <c r="D49" t="n">
-        <v>-9.19726985176425e-07</v>
+        <v>-5.43066003764652e-07</v>
       </c>
     </row>
     <row r="50">
@@ -1118,10 +1119,10 @@
         <v>-0.03030303030303028</v>
       </c>
       <c r="C50" t="n">
-        <v>-3.991360339972633e-07</v>
+        <v>-6.437901279049502e-07</v>
       </c>
       <c r="D50" t="n">
-        <v>-3.991360339972633e-07</v>
+        <v>-6.437901279049502e-07</v>
       </c>
     </row>
     <row r="51">
@@ -1132,10 +1133,10 @@
         <v>-0.01010101010101006</v>
       </c>
       <c r="C51" t="n">
-        <v>-1.992616111456932e-08</v>
+        <v>-1.958700943974309e-08</v>
       </c>
       <c r="D51" t="n">
-        <v>-1.992616111456932e-08</v>
+        <v>-1.958700943974309e-08</v>
       </c>
     </row>
     <row r="52">
@@ -1146,10 +1147,10 @@
         <v>0.01010101010101017</v>
       </c>
       <c r="C52" t="n">
-        <v>1.808548200119853e-07</v>
+        <v>3.939376127230211e-07</v>
       </c>
       <c r="D52" t="n">
-        <v>1.808548200119853e-07</v>
+        <v>3.939376127230211e-07</v>
       </c>
     </row>
     <row r="53">
@@ -1160,10 +1161,10 @@
         <v>0.0303030303030305</v>
       </c>
       <c r="C53" t="n">
-        <v>8.525981823165029e-07</v>
+        <v>8.280768654662008e-07</v>
       </c>
       <c r="D53" t="n">
-        <v>8.525981823165029e-07</v>
+        <v>8.280768654662008e-07</v>
       </c>
     </row>
     <row r="54">
@@ -1174,10 +1175,10 @@
         <v>0.05050505050505061</v>
       </c>
       <c r="C54" t="n">
-        <v>1.11383511582097e-06</v>
+        <v>1.304714413548619e-06</v>
       </c>
       <c r="D54" t="n">
-        <v>1.11383511582097e-06</v>
+        <v>1.304714413548619e-06</v>
       </c>
     </row>
     <row r="55">
@@ -1188,10 +1189,10 @@
         <v>0.07070707070707072</v>
       </c>
       <c r="C55" t="n">
-        <v>1.73738549411064e-06</v>
+        <v>1.837893237028521e-06</v>
       </c>
       <c r="D55" t="n">
-        <v>1.73738549411064e-06</v>
+        <v>1.837893237028521e-06</v>
       </c>
     </row>
     <row r="56">
@@ -1202,10 +1203,10 @@
         <v>0.09090909090909105</v>
       </c>
       <c r="C56" t="n">
-        <v>3.125216152899807e-06</v>
+        <v>2.784119801944137e-06</v>
       </c>
       <c r="D56" t="n">
-        <v>3.125216152899807e-06</v>
+        <v>2.784119801944137e-06</v>
       </c>
     </row>
     <row r="57">
@@ -1216,10 +1217,10 @@
         <v>0.1111111111111112</v>
       </c>
       <c r="C57" t="n">
-        <v>4.098361886842276e-06</v>
+        <v>4.122834459589217e-06</v>
       </c>
       <c r="D57" t="n">
-        <v>4.098361886842276e-06</v>
+        <v>4.122834459589217e-06</v>
       </c>
     </row>
     <row r="58">
@@ -1230,10 +1231,10 @@
         <v>0.1313131313131315</v>
       </c>
       <c r="C58" t="n">
-        <v>5.549792581675445e-06</v>
+        <v>5.417183929522101e-06</v>
       </c>
       <c r="D58" t="n">
-        <v>5.549792581675445e-06</v>
+        <v>5.417183929522101e-06</v>
       </c>
     </row>
     <row r="59">
@@ -1244,10 +1245,10 @@
         <v>0.1515151515151516</v>
       </c>
       <c r="C59" t="n">
-        <v>7.270216411266156e-06</v>
+        <v>7.15820828727419e-06</v>
       </c>
       <c r="D59" t="n">
-        <v>7.270216411266156e-06</v>
+        <v>7.15820828727419e-06</v>
       </c>
     </row>
     <row r="60">
@@ -1258,10 +1259,10 @@
         <v>0.1717171717171717</v>
       </c>
       <c r="C60" t="n">
-        <v>9.003892450355395e-06</v>
+        <v>9.237367309533017e-06</v>
       </c>
       <c r="D60" t="n">
-        <v>9.003892450355395e-06</v>
+        <v>9.237367309533017e-06</v>
       </c>
     </row>
     <row r="61">
@@ -1272,10 +1273,10 @@
         <v>0.191919191919192</v>
       </c>
       <c r="C61" t="n">
-        <v>1.160449428522706e-05</v>
+        <v>1.141838198129526e-05</v>
       </c>
       <c r="D61" t="n">
-        <v>1.160449428522706e-05</v>
+        <v>1.141838198129526e-05</v>
       </c>
     </row>
     <row r="62">
@@ -1286,10 +1287,10 @@
         <v>0.2121212121212122</v>
       </c>
       <c r="C62" t="n">
-        <v>1.475147635287789e-05</v>
+        <v>1.477296309421333e-05</v>
       </c>
       <c r="D62" t="n">
-        <v>1.475147635287789e-05</v>
+        <v>1.477296309421333e-05</v>
       </c>
     </row>
     <row r="63">
@@ -1300,10 +1301,10 @@
         <v>0.2323232323232325</v>
       </c>
       <c r="C63" t="n">
-        <v>1.838099940959834e-05</v>
+        <v>1.827172832546189e-05</v>
       </c>
       <c r="D63" t="n">
-        <v>1.838099940959834e-05</v>
+        <v>1.827172832546189e-05</v>
       </c>
     </row>
     <row r="64">
@@ -1314,10 +1315,10 @@
         <v>0.2525252525252526</v>
       </c>
       <c r="C64" t="n">
-        <v>2.283152857261598e-05</v>
+        <v>2.3004458911557e-05</v>
       </c>
       <c r="D64" t="n">
-        <v>2.283152857261598e-05</v>
+        <v>2.3004458911557e-05</v>
       </c>
     </row>
     <row r="65">
@@ -1328,10 +1329,10 @@
         <v>0.2727272727272729</v>
       </c>
       <c r="C65" t="n">
-        <v>2.867891267740074e-05</v>
+        <v>2.873051829489354e-05</v>
       </c>
       <c r="D65" t="n">
-        <v>2.867891267740074e-05</v>
+        <v>2.873051829489354e-05</v>
       </c>
     </row>
     <row r="66">
@@ -1342,10 +1343,10 @@
         <v>0.292929292929293</v>
       </c>
       <c r="C66" t="n">
-        <v>3.539768343232192e-05</v>
+        <v>3.537462167110956e-05</v>
       </c>
       <c r="D66" t="n">
-        <v>3.539768343232192e-05</v>
+        <v>3.537462167110956e-05</v>
       </c>
     </row>
     <row r="67">
@@ -1356,10 +1357,10 @@
         <v>0.3131313131313131</v>
       </c>
       <c r="C67" t="n">
-        <v>4.402698812895e-05</v>
+        <v>4.385045611248921e-05</v>
       </c>
       <c r="D67" t="n">
-        <v>4.402698812895e-05</v>
+        <v>4.385045611248921e-05</v>
       </c>
     </row>
     <row r="68">
@@ -1370,10 +1371,10 @@
         <v>0.3333333333333335</v>
       </c>
       <c r="C68" t="n">
-        <v>5.392958138709982e-05</v>
+        <v>5.37849906112078e-05</v>
       </c>
       <c r="D68" t="n">
-        <v>5.392958138709982e-05</v>
+        <v>5.37849906112078e-05</v>
       </c>
     </row>
     <row r="69">
@@ -1384,10 +1385,10 @@
         <v>0.3535353535353536</v>
       </c>
       <c r="C69" t="n">
-        <v>6.655642361756346e-05</v>
+        <v>6.654501115820521e-05</v>
       </c>
       <c r="D69" t="n">
-        <v>6.655642361756346e-05</v>
+        <v>6.654501115820521e-05</v>
       </c>
     </row>
     <row r="70">
@@ -1398,10 +1399,10 @@
         <v>0.3737373737373739</v>
       </c>
       <c r="C70" t="n">
-        <v>8.190102498436747e-05</v>
+        <v>8.176471964936492e-05</v>
       </c>
       <c r="D70" t="n">
-        <v>8.190102498436747e-05</v>
+        <v>8.176471964936492e-05</v>
       </c>
     </row>
     <row r="71">
@@ -1412,10 +1413,10 @@
         <v>0.393939393939394</v>
       </c>
       <c r="C71" t="n">
-        <v>0.0001009121026161246</v>
+        <v>0.0001009735746998154</v>
       </c>
       <c r="D71" t="n">
-        <v>0.0001009121026161246</v>
+        <v>0.0001009735746998154</v>
       </c>
     </row>
     <row r="72">
@@ -1426,10 +1427,10 @@
         <v>0.4141414141414144</v>
       </c>
       <c r="C72" t="n">
-        <v>0.000123835561085966</v>
+        <v>0.0001237915802506822</v>
       </c>
       <c r="D72" t="n">
-        <v>0.000123835561085966</v>
+        <v>0.0001237915802506822</v>
       </c>
     </row>
     <row r="73">
@@ -1440,10 +1441,10 @@
         <v>0.4343434343434345</v>
       </c>
       <c r="C73" t="n">
-        <v>0.0001519471079867747</v>
+        <v>0.000151973100795235</v>
       </c>
       <c r="D73" t="n">
-        <v>0.0001519471079867747</v>
+        <v>0.000151973100795235</v>
       </c>
     </row>
     <row r="74">
@@ -1454,10 +1455,10 @@
         <v>0.4545454545454546</v>
       </c>
       <c r="C74" t="n">
-        <v>0.0001863871311902533</v>
+        <v>0.0001860857699164764</v>
       </c>
       <c r="D74" t="n">
-        <v>0.0001863871311902533</v>
+        <v>0.0001860857699164764</v>
       </c>
     </row>
     <row r="75">
@@ -1468,10 +1469,10 @@
         <v>0.4747474747474749</v>
       </c>
       <c r="C75" t="n">
-        <v>0.0002284395034810829</v>
+        <v>0.0002281485839100634</v>
       </c>
       <c r="D75" t="n">
-        <v>0.0002284395034810829</v>
+        <v>0.0002281485839100634</v>
       </c>
     </row>
     <row r="76">
@@ -1482,10 +1483,10 @@
         <v>0.494949494949495</v>
       </c>
       <c r="C76" t="n">
-        <v>0.0002803934575444</v>
+        <v>0.0002800345526424824</v>
       </c>
       <c r="D76" t="n">
-        <v>0.0002803934575444</v>
+        <v>0.0002800345526424824</v>
       </c>
     </row>
     <row r="77">
@@ -1496,10 +1497,10 @@
         <v>0.5151515151515154</v>
       </c>
       <c r="C77" t="n">
-        <v>0.0003432804583753863</v>
+        <v>0.0003430382593146974</v>
       </c>
       <c r="D77" t="n">
-        <v>0.0003432804583753863</v>
+        <v>0.0003430382593146974</v>
       </c>
     </row>
     <row r="78">
@@ -1510,10 +1511,10 @@
         <v>0.5353535353535355</v>
       </c>
       <c r="C78" t="n">
-        <v>0.0004204230526674805</v>
+        <v>0.0004208362507097259</v>
       </c>
       <c r="D78" t="n">
-        <v>0.0004204230526674805</v>
+        <v>0.0004208362507097259</v>
       </c>
     </row>
     <row r="79">
@@ -1524,10 +1525,10 @@
         <v>0.5555555555555556</v>
       </c>
       <c r="C79" t="n">
-        <v>0.0005154887857214339</v>
+        <v>0.0005155257830554668</v>
       </c>
       <c r="D79" t="n">
-        <v>0.0005154887857214339</v>
+        <v>0.0005155257830554668</v>
       </c>
     </row>
     <row r="80">
@@ -1538,10 +1539,10 @@
         <v>0.5757575757575759</v>
       </c>
       <c r="C80" t="n">
-        <v>0.0006311584152654783</v>
+        <v>0.0006313016539495806</v>
       </c>
       <c r="D80" t="n">
-        <v>0.0006311584152654783</v>
+        <v>0.0006313016539495806</v>
       </c>
     </row>
     <row r="81">
@@ -1552,10 +1553,10 @@
         <v>0.595959595959596</v>
       </c>
       <c r="C81" t="n">
-        <v>0.0007728510181668379</v>
+        <v>0.0007727161256274545</v>
       </c>
       <c r="D81" t="n">
-        <v>0.0007728510181668379</v>
+        <v>0.0007727161256274545</v>
       </c>
     </row>
     <row r="82">
@@ -1566,10 +1567,10 @@
         <v>0.6161616161616164</v>
       </c>
       <c r="C82" t="n">
-        <v>0.000946312203622447</v>
+        <v>0.0009458599846723095</v>
       </c>
       <c r="D82" t="n">
-        <v>0.000946312203622447</v>
+        <v>0.0009458599846723095</v>
       </c>
     </row>
     <row r="83">
@@ -1580,10 +1581,10 @@
         <v>0.6363636363636365</v>
       </c>
       <c r="C83" t="n">
-        <v>0.001158447162482619</v>
+        <v>0.001159027921753709</v>
       </c>
       <c r="D83" t="n">
-        <v>0.001158447162482619</v>
+        <v>0.001159027921753709</v>
       </c>
     </row>
     <row r="84">
@@ -1594,10 +1595,10 @@
         <v>0.6565656565656568</v>
       </c>
       <c r="C84" t="n">
-        <v>0.001418455920629685</v>
+        <v>0.001418326342114189</v>
       </c>
       <c r="D84" t="n">
-        <v>0.001418455920629685</v>
+        <v>0.001418326342114189</v>
       </c>
     </row>
     <row r="85">
@@ -1608,10 +1609,10 @@
         <v>0.6767676767676769</v>
       </c>
       <c r="C85" t="n">
-        <v>0.001736607696385914</v>
+        <v>0.001736228963631825</v>
       </c>
       <c r="D85" t="n">
-        <v>0.001736607696385914</v>
+        <v>0.001736228963631825</v>
       </c>
     </row>
     <row r="86">
@@ -1622,10 +1623,10 @@
         <v>0.696969696969697</v>
       </c>
       <c r="C86" t="n">
-        <v>0.002125779352700327</v>
+        <v>0.002125889147693581</v>
       </c>
       <c r="D86" t="n">
-        <v>0.002125779352700327</v>
+        <v>0.002125889147693581</v>
       </c>
     </row>
     <row r="87">
@@ -1636,10 +1637,10 @@
         <v>0.7171717171717173</v>
       </c>
       <c r="C87" t="n">
-        <v>0.002601783646772193</v>
+        <v>0.00260227566181072</v>
       </c>
       <c r="D87" t="n">
-        <v>0.002601783646772193</v>
+        <v>0.00260227566181072</v>
       </c>
     </row>
     <row r="88">
@@ -1650,10 +1651,10 @@
         <v>0.7373737373737375</v>
       </c>
       <c r="C88" t="n">
-        <v>0.003185078652632825</v>
+        <v>0.003184981855053522</v>
       </c>
       <c r="D88" t="n">
-        <v>0.003185078652632825</v>
+        <v>0.003184981855053522</v>
       </c>
     </row>
     <row r="89">
@@ -1664,10 +1665,10 @@
         <v>0.7575757575757578</v>
       </c>
       <c r="C89" t="n">
-        <v>0.003898673210266907</v>
+        <v>0.003898582305030314</v>
       </c>
       <c r="D89" t="n">
-        <v>0.003898673210266907</v>
+        <v>0.003898582305030314</v>
       </c>
     </row>
     <row r="90">
@@ -1678,10 +1679,10 @@
         <v>0.7777777777777779</v>
       </c>
       <c r="C90" t="n">
-        <v>0.004771849070328257</v>
+        <v>0.004772013222051238</v>
       </c>
       <c r="D90" t="n">
-        <v>0.004771849070328257</v>
+        <v>0.004772013222051238</v>
       </c>
     </row>
     <row r="91">
@@ -1692,10 +1693,10 @@
         <v>0.7979797979797982</v>
       </c>
       <c r="C91" t="n">
-        <v>0.005841024600406635</v>
+        <v>0.005840599309315015</v>
       </c>
       <c r="D91" t="n">
-        <v>0.005841024600406635</v>
+        <v>0.005840599309315015</v>
       </c>
     </row>
     <row r="92">
@@ -1706,10 +1707,10 @@
         <v>0.8181818181818183</v>
       </c>
       <c r="C92" t="n">
-        <v>0.007148508534971624</v>
+        <v>0.007149114091210143</v>
       </c>
       <c r="D92" t="n">
-        <v>0.007148508534971624</v>
+        <v>0.007149114091210143</v>
       </c>
     </row>
     <row r="93">
@@ -1720,10 +1721,10 @@
         <v>0.8383838383838385</v>
       </c>
       <c r="C93" t="n">
-        <v>0.008749587284016622</v>
+        <v>0.008749354732737942</v>
       </c>
       <c r="D93" t="n">
-        <v>0.008749587284016622</v>
+        <v>0.008749354732737942</v>
       </c>
     </row>
     <row r="94">
@@ -1734,10 +1735,10 @@
         <v>0.8585858585858588</v>
       </c>
       <c r="C94" t="n">
-        <v>0.01070886720236716</v>
+        <v>0.01070859678191671</v>
       </c>
       <c r="D94" t="n">
-        <v>0.01070886720236716</v>
+        <v>0.01070859678191671</v>
       </c>
     </row>
     <row r="95">
@@ -1748,10 +1749,10 @@
         <v>0.8787878787878789</v>
       </c>
       <c r="C95" t="n">
-        <v>0.01310667710960612</v>
+        <v>0.01310686664860007</v>
       </c>
       <c r="D95" t="n">
-        <v>0.01310667710960612</v>
+        <v>0.01310686664860007</v>
       </c>
     </row>
     <row r="96">
@@ -1762,10 +1763,10 @@
         <v>0.8989898989898992</v>
       </c>
       <c r="C96" t="n">
-        <v>0.0160415012852845</v>
+        <v>0.01604105004148495</v>
       </c>
       <c r="D96" t="n">
-        <v>0.0160415012852845</v>
+        <v>0.01604105004148495</v>
       </c>
     </row>
     <row r="97">
@@ -1776,10 +1777,10 @@
         <v>0.9191919191919193</v>
       </c>
       <c r="C97" t="n">
-        <v>0.01963309229947683</v>
+        <v>0.01963236071438248</v>
       </c>
       <c r="D97" t="n">
-        <v>0.01963309229947683</v>
+        <v>0.01963236071438248</v>
       </c>
     </row>
     <row r="98">
@@ -1790,10 +1791,10 @@
         <v>0.9393939393939394</v>
       </c>
       <c r="C98" t="n">
-        <v>0.02402883572353023</v>
+        <v>0.02402868164071549</v>
       </c>
       <c r="D98" t="n">
-        <v>0.02402883572353023</v>
+        <v>0.02402868164071549</v>
       </c>
     </row>
     <row r="99">
@@ -1804,10 +1805,10 @@
         <v>0.9595959595959598</v>
       </c>
       <c r="C99" t="n">
-        <v>0.0294083192729611</v>
+        <v>0.0294085709139681</v>
       </c>
       <c r="D99" t="n">
-        <v>0.0294083192729611</v>
+        <v>0.0294085709139681</v>
       </c>
     </row>
     <row r="100">
@@ -1818,10 +1819,10 @@
         <v>0.9797979797979799</v>
       </c>
       <c r="C100" t="n">
-        <v>0.03599246065959427</v>
+        <v>0.03599274546826096</v>
       </c>
       <c r="D100" t="n">
-        <v>0.03599246065959427</v>
+        <v>0.03599274546826096</v>
       </c>
     </row>
     <row r="101">
@@ -1832,10 +1833,46 @@
         <v>1</v>
       </c>
       <c r="C101" t="n">
-        <v>0.04405069569657915</v>
+        <v>0.04405102465484474</v>
       </c>
       <c r="D101" t="n">
-        <v>0.04405069569657915</v>
+        <v>0.04405102465484474</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Fecha y hora inicio</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Isc</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-07-04 10:00:00</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>53.1</v>
       </c>
     </row>
   </sheetData>
